--- a/knowledge/passwords.xlsx
+++ b/knowledge/passwords.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,41 +435,24 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>School WiFi Login</v>
+        <v>Windows Admin</v>
       </c>
       <c r="B3" t="str">
-        <v>Staff</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>223344@55</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v>Captive portal after WiFi connect</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Windows Admin</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
         <v>Add details here</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>